--- a/web/public/forms/orig/o-gangu-taseol.xlsx
+++ b/web/public/forms/orig/o-gangu-taseol.xlsx
@@ -4,9 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAMSUNG\Downloads\"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CB8882-790F-47AA-9BA2-E0C1A90ABA9F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>

--- a/web/public/forms/orig/o-gangu-taseol.xlsx
+++ b/web/public/forms/orig/o-gangu-taseol.xlsx
@@ -747,7 +747,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="51" t="inlineStr">

--- a/web/public/forms/orig/o-gangu-taseol.xlsx
+++ b/web/public/forms/orig/o-gangu-taseol.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계획서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-계획서" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'계획서'!$A$1:$H$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'예시-계획서'!$A$1:$H$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -229,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -362,9 +360,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -788,10 +783,7 @@
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="8">
-        <f>IF(N(C5)=0,"","("&amp;CHOOSE(WEEKDAY(C5),"일","월","화","수","목","금","토")&amp;"요일)")</f>
-        <v/>
-      </c>
+      <c r="F5" s="8" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
@@ -828,10 +820,7 @@
           <t>계획 시간</t>
         </is>
       </c>
-      <c r="G7" s="12">
-        <f>IF(OR(N(C7)=0,N(E7)=0),"",ROUND((E7-C7)*24,2))</f>
-        <v/>
-      </c>
+      <c r="G7" s="12" t="n"/>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
@@ -842,10 +831,7 @@
       </c>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="13" t="n"/>
-      <c r="D8" s="14">
-        <f>"맑음 ("&amp;IF(C8="맑음","○","  ")&amp;")"&amp;"  ·  "&amp;"흐림 ("&amp;IF(C8="흐림","○","  ")&amp;")"&amp;"  ·  "&amp;"우천 ("&amp;IF(C8="우천","○","  ")&amp;")"</f>
-        <v/>
-      </c>
+      <c r="D8" s="14" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="11" t="inlineStr">
@@ -863,10 +849,7 @@
       </c>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="13" t="n"/>
-      <c r="D9" s="14">
-        <f>"해당없음 ("&amp;IF(C9="해당없음","○","  ")&amp;")"&amp;"  ·  "&amp;"강우 ("&amp;IF(C9="강우","○","  ")&amp;")"&amp;"  ·  "&amp;"강설 ("&amp;IF(C9="강설","○","  ")&amp;")"</f>
-        <v/>
-      </c>
+      <c r="D9" s="14" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="11" t="inlineStr">
@@ -952,10 +935,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n"/>
-      <c r="C14" s="22">
-        <f>IF(OR(N(G11)=0,N(G14)=0),"",ROUNDUP(G11/G14,0))</f>
-        <v/>
-      </c>
+      <c r="C14" s="22" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="11" t="inlineStr">
         <is>
@@ -1016,22 +996,13 @@
           <t>예상 시간</t>
         </is>
       </c>
-      <c r="H16" s="12">
-        <f>IF(OR(N(G11)=0,N(F15)=0,N(F16)=0),"",ROUND(G11/(F15*F16),2))</f>
-        <v/>
-      </c>
+      <c r="H16" s="12" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="28">
-        <f>IF(OR(H16="",G7=""),"",IF(H16&gt;G7,"⚠ 예상 타설시간("&amp;H16&amp;"시간)이 계획 타설시간("&amp;G7&amp;"시간)보다 깁니다 — 펌프카를 늘리거나 타설시간을 다시 잡으세요.",""))</f>
-        <v/>
-      </c>
+      <c r="A17" s="28" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="11">
-        <f>"투입인원"&amp;IF(N(D18)+N(F18)+N(H18)=0,"",CHAR(10)&amp;"(계 "&amp;(N(D18)+N(F18)+N(H18))&amp;"명)")</f>
-        <v/>
-      </c>
+      <c r="A18" s="11" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="17" t="inlineStr">
         <is>
@@ -1141,10 +1112,7 @@
       <c r="H21" s="5" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="28">
-        <f>IF(OR(C9="강우",C9="강설"),IF(COUNTIF(C19:F19,"■*")+COUNTIF(C20:E20,"■*")+COUNTIF(C21:F21,"■*")=0,"⚠ 강우·강설 예보입니다 — 보양방법·이음대책·양생방법을 고르세요.",IF(OR(COUNTIF(C19:F19,"■*")=0,COUNTIF(C20:E20,"■*")=0,COUNTIF(C21:F21,"■*")=0),"⚠ 강우·강설 예보입니다 — 보양방법·이음대책·양생방법 가운데 안 고른 것이 있습니다.","")),"")</f>
-        <v/>
-      </c>
+      <c r="A22" s="28" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1160,10 +1128,7 @@
       </c>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="31" t="n"/>
-      <c r="F23" s="32">
-        <f>IF(OR(N(G11)=0,N(G23)=0),"","권장 "&amp;MAX(1,ROUNDUP(G11/G23,0))&amp;"회")</f>
-        <v/>
-      </c>
+      <c r="F23" s="32" t="n"/>
       <c r="G23" s="33" t="n">
         <v>120</v>
       </c>
@@ -1177,10 +1142,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n"/>
-      <c r="C24" s="14">
-        <f>IF(H8="","",IF(H8&gt;=25,"1.5시간 이내 (외기온 25℃ 이상)","2시간 이내 (외기온 25℃ 미만)")&amp;" — 콘크리트 표준시방서 KCS 14 20 10")</f>
-        <v/>
-      </c>
+      <c r="C24" s="14" t="n"/>
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
@@ -1352,6 +1314,7 @@
       <c r="G34" s="48" t="n"/>
       <c r="H34" s="49" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="50" t="inlineStr">
         <is>
@@ -1473,813 +1436,4 @@
   <pageMargins left="0.5" right="0.5" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="E1" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="38" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>강우 시 콘크리트 타설 계획서</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="4" customHeight="1"/>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>공 사 명</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>타설일자</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="7" t="n">
-        <v>46191</v>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="8">
-        <f>IF(N(C5)=0,"","("&amp;CHOOSE(WEEKDAY(C5),"일","월","화","수","목","금","토")&amp;"요일)")</f>
-        <v/>
-      </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>타설위치 및 부위</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>PC 암거 기초 슬래브 STA.0+120 ~ 0+200</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>타설시간</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="9" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>계획 시간</t>
-        </is>
-      </c>
-      <c r="G7" s="12">
-        <f>IF(OR(N(C7)=0,N(E7)=0),"",ROUND((E7-C7)*24,2))</f>
-        <v/>
-      </c>
-      <c r="H7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>예상날씨</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>흐림</t>
-        </is>
-      </c>
-      <c r="D8" s="14">
-        <f>"맑음 ("&amp;IF(C8="맑음","○","  ")&amp;")"&amp;"  ·  "&amp;"흐림 ("&amp;IF(C8="흐림","○","  ")&amp;")"&amp;"  ·  "&amp;"우천 ("&amp;IF(C8="우천","○","  ")&amp;")"</f>
-        <v/>
-      </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>예상기온</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>강우여부</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>강우</t>
-        </is>
-      </c>
-      <c r="D9" s="14">
-        <f>"해당없음 ("&amp;IF(C9="해당없음","○","  ")&amp;")"&amp;"  ·  "&amp;"강우 ("&amp;IF(C9="강우","○","  ")&amp;")"&amp;"  ·  "&amp;"강설 ("&amp;IF(C9="강설","○","  ")&amp;")"</f>
-        <v/>
-      </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>강우 확률</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>예상 강우량
-(전일 예보 기준)</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>시간당</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>하루</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>CON'C 규격</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>25 - 24 - 150</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>타설 예상수량</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="20" t="n">
-        <v>86</v>
-      </c>
-      <c r="H11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>레미콘 공급업체명</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>예시레미콘(주)</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>운반거리</t>
-        </is>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="21" t="n"/>
-      <c r="H13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>레미콘 대수</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="22">
-        <f>IF(OR(N(G11)=0,N(G14)=0),"",ROUNDUP(G11/G14,0))</f>
-        <v/>
-      </c>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>1대 적재량</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>타설방법 및 장비</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>진동기</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>펌프카</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>백호</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>직접타설</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="26" t="inlineStr">
-        <is>
-          <t>펌프 타설량</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>25</v>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>예상 시간</t>
-        </is>
-      </c>
-      <c r="H16" s="12">
-        <f>IF(OR(N(G11)=0,N(F15)=0,N(F16)=0),"",ROUND(G11/(F15*F16),2))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="28">
-        <f>IF(OR(H16="",G7=""),"",IF(H16&gt;G7,"⚠ 예상 타설시간("&amp;H16&amp;"시간)이 계획 타설시간("&amp;G7&amp;"시간)보다 깁니다 — 펌프카를 늘리거나 타설시간을 다시 잡으세요.",""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="11">
-        <f>"투입인원"&amp;IF(N(D18)+N(F18)+N(H18)=0,"",CHAR(10)&amp;"(계 "&amp;(N(D18)+N(F18)+N(H18))&amp;"명)")</f>
-        <v/>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>CON'C공</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>형틀공</t>
-        </is>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>보통인부</t>
-        </is>
-      </c>
-      <c r="H18" s="25" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>보양방법
-(강우 시)</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="29" t="inlineStr">
-        <is>
-          <t>□ 해당없음</t>
-        </is>
-      </c>
-      <c r="D19" s="29" t="inlineStr">
-        <is>
-          <t>■ 호퍼외부천막</t>
-        </is>
-      </c>
-      <c r="E19" s="29" t="inlineStr">
-        <is>
-          <t>■ 비닐시트</t>
-        </is>
-      </c>
-      <c r="F19" s="29" t="inlineStr">
-        <is>
-          <t>□ 기타</t>
-        </is>
-      </c>
-      <c r="G19" s="30" t="n"/>
-      <c r="H19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>타설중 중단시
-이음대책</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="29" t="inlineStr">
-        <is>
-          <t>■ PVC 타설막이</t>
-        </is>
-      </c>
-      <c r="D20" s="29" t="inlineStr">
-        <is>
-          <t>□ 전단보강근</t>
-        </is>
-      </c>
-      <c r="E20" s="29" t="inlineStr">
-        <is>
-          <t>□ 기타</t>
-        </is>
-      </c>
-      <c r="F20" s="30" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>양생방법</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="29" t="inlineStr">
-        <is>
-          <t>■ 비닐시트보양</t>
-        </is>
-      </c>
-      <c r="D21" s="29" t="inlineStr">
-        <is>
-          <t>□ 보온천막보양</t>
-        </is>
-      </c>
-      <c r="E21" s="29" t="inlineStr">
-        <is>
-          <t>□ 열풍기</t>
-        </is>
-      </c>
-      <c r="F21" s="29" t="inlineStr">
-        <is>
-          <t>□ 쇠흙손미장</t>
-        </is>
-      </c>
-      <c r="G21" s="30" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="28">
-        <f>IF(OR(C9="강우",C9="강설"),IF(COUNTIF(C19:F19,"■*")+COUNTIF(C20:E20,"■*")+COUNTIF(C21:F21,"■*")=0,"⚠ 강우·강설 예보입니다 — 보양방법·이음대책·양생방법을 고르세요.",IF(OR(COUNTIF(C19:F19,"■*")=0,COUNTIF(C20:E20,"■*")=0,COUNTIF(C21:F21,"■*")=0),"⚠ 강우·강설 예보입니다 — 보양방법·이음대책·양생방법 가운데 안 고른 것이 있습니다.","")),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>품질시험 및 회수</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>콘크리트 물성시험</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="32">
-        <f>IF(OR(N(G11)=0,N(G23)=0),"","권장 "&amp;MAX(1,ROUNDUP(G11/G23,0))&amp;"회")</f>
-        <v/>
-      </c>
-      <c r="G23" s="33" t="n">
-        <v>120</v>
-      </c>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>비비기~타설 끝
-시간 한도</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="14">
-        <f>IF(H8="","",IF(H8&gt;=25,"1.5시간 이내 (외기온 25℃ 이상)","2시간 이내 (외기온 25℃ 미만)")&amp;" — 콘크리트 표준시방서 KCS 14 20 10")</f>
-        <v/>
-      </c>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>특기사항</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="34" t="inlineStr">
-        <is>
-          <t>타설 중 시간당 강우 5mm 이상이면 타설을 멈추고 이음부를 처리한 뒤 감리원과 다시 협의</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="35" t="inlineStr">
-        <is>
-          <t>감리원 :</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>김감리</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-      <c r="F26" s="35" t="inlineStr">
-        <is>
-          <t>감리원 :</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="n"/>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="35" t="inlineStr">
-        <is>
-          <t>감리원 :</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-      <c r="F27" s="35" t="inlineStr">
-        <is>
-          <t>감리원 :</t>
-        </is>
-      </c>
-      <c r="G27" s="13" t="n"/>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="36" t="inlineStr">
-        <is>
-          <t>첨부: 타설부위 도면, 장비배치도, 기상청 일기예보</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="6" customHeight="1"/>
-    <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="37" t="inlineStr">
-        <is>
-          <t>상기와 같이 콘크리트 타설 계획서를
-제출합니다.</t>
-        </is>
-      </c>
-      <c r="B30" s="38" t="n"/>
-      <c r="C30" s="38" t="n"/>
-      <c r="D30" s="39" t="n"/>
-      <c r="E30" s="37" t="inlineStr">
-        <is>
-          <t>상기와 같이 콘크리트 타설 계획서에 의한
-콘크리트 타설을 승인합니다.</t>
-        </is>
-      </c>
-      <c r="F30" s="38" t="n"/>
-      <c r="G30" s="38" t="n"/>
-      <c r="H30" s="39" t="n"/>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="40" t="n">
-        <v>46190</v>
-      </c>
-      <c r="B31" s="41" t="n"/>
-      <c r="C31" s="41" t="n"/>
-      <c r="D31" s="42" t="n"/>
-      <c r="E31" s="40" t="n">
-        <v>46190</v>
-      </c>
-      <c r="F31" s="41" t="n"/>
-      <c r="G31" s="41" t="n"/>
-      <c r="H31" s="42" t="n"/>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="43" t="n"/>
-      <c r="B32" s="41" t="n"/>
-      <c r="C32" s="41" t="n"/>
-      <c r="D32" s="42" t="n"/>
-      <c r="E32" s="43" t="n"/>
-      <c r="F32" s="41" t="n"/>
-      <c r="G32" s="41" t="n"/>
-      <c r="H32" s="42" t="n"/>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="44" t="inlineStr">
-        <is>
-          <t>현장대리인 :</t>
-        </is>
-      </c>
-      <c r="B33" s="45" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="C33" s="41" t="n"/>
-      <c r="D33" s="46" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-      <c r="E33" s="44" t="inlineStr">
-        <is>
-          <t>책임기술인 :</t>
-        </is>
-      </c>
-      <c r="F33" s="45" t="inlineStr">
-        <is>
-          <t>박책임</t>
-        </is>
-      </c>
-      <c r="G33" s="41" t="n"/>
-      <c r="H33" s="46" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="8" customHeight="1">
-      <c r="A34" s="47" t="n"/>
-      <c r="B34" s="48" t="n"/>
-      <c r="C34" s="48" t="n"/>
-      <c r="D34" s="49" t="n"/>
-      <c r="E34" s="47" t="n"/>
-      <c r="F34" s="48" t="n"/>
-      <c r="G34" s="48" t="n"/>
-      <c r="H34" s="49" t="n"/>
-    </row>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="50" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사 · 회사 · 사람).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A25:B28"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A9:B9"/>
-  </mergeCells>
-  <dataValidations count="13">
-    <dataValidation sqref="C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"맑음,흐림,우천"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"해당없음,강우,강설"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"□ 해당없음,■ 해당없음"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"□ 호퍼외부천막,■ 호퍼외부천막"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"□ 비닐시트,■ 비닐시트"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"□ 기타,■ 기타"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"□ PVC 타설막이,■ PVC 타설막이"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"□ 전단보강근,■ 전단보강근"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"□ 기타,■ 기타"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"□ 비닐시트보양,■ 비닐시트보양"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"□ 보온천막보양,■ 보온천막보양"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"□ 열풍기,■ 열풍기"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"□ 쇠흙손미장,■ 쇠흙손미장"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/orig/o-gangu-taseol.xlsx
+++ b/web/public/forms/orig/o-gangu-taseol.xlsx
@@ -742,7 +742,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
